--- a/examples/STUDY01_TRAIL01/outputs/reports/all_closed.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/reports/all_closed.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -38,7 +40,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -52,7 +54,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -73,13 +80,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -450,7 +461,7 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -467,7 +478,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 14:31</t>
+          <t>Last run: 23Apr2026 17:08</t>
         </is>
       </c>
     </row>
@@ -502,22 +513,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Invalid dose form - not in allowed list</t>
+          <t>No issues found</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ECCHK004</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -537,10 +548,10 @@
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -556,95 +567,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 14:31</t>
+          <t>Last run: 23Apr2026 17:08</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>CHECK ID</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>SUBJECT ID</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>VISIT ID</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>FIND DATE</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>ANALYST NOTE</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>ANALYST ID</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>REVIEW NOTE</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>REVIEWER ID</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>ECCHK004</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>SUBJ-007</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n">
-        <v>500</v>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Dose form 'INJECTION' not in allowed list (TABLET/CAPSULE) for treatment: DRUG A 20MG at visit END OF TREATMENT</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>[closed by reviewer]</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>No issues found</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>This is empty</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr"/>
+      <c r="J4" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/STUDY01_TRAIL01/outputs/reports/all_closed.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/reports/all_closed.xlsx
@@ -54,17 +54,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00203864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EAF1DD"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,17 +80,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -458,10 +463,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="5" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -478,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 17:08</t>
+          <t>Last run: 23Apr2026 18:07</t>
         </is>
       </c>
     </row>
@@ -513,22 +518,64 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>No issues found</t>
+          <t>AE end date before start date</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>AECHK001</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invalid dose form - not in allowed list</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ECCHK004</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Missing administration status (ECSTAT)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ECCHK005</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -542,16 +589,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
@@ -567,95 +614,205 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 17:08</t>
+          <t>Last run: 23Apr2026 18:07</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CHECK ID</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>SUBJECT ID</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>VISIT ID</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>FIND DATE</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>STATUS</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>ANALYST NOTE</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>ANALYST ID</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>REVIEW NOTE</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="J3" s="4" t="inlineStr">
         <is>
           <t>REVIEWER ID</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>No issues found</t>
-        </is>
-      </c>
-      <c r="E4" s="7" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>AECHK001</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>SUBJ-002</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>AE end date (26Mar2023) is before start date (31Mar2023) for term: DIZZINESS (AESEQ=7)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
         <v>46135</v>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>This is empty</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr"/>
-      <c r="I4" s="6" t="inlineStr"/>
-      <c r="J4" s="6" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>[closed by reviewer]</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>star</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>warrier</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>god</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>ECCHK004</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>SUBJ-007</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 20MG at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">what </t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">you </t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">are </t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>doing</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>ECCHK005</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>SUBJ-005</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Administration status (ECSTAT) is missing for treatment: DRUG A 10MG at visit END OF TREATMENT</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>46135</v>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>yeah</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> wow</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">so </t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
+        <is>
+          <t>ju</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/examples/STUDY01_TRAIL01/outputs/reports/all_closed.xlsx
+++ b/examples/STUDY01_TRAIL01/outputs/reports/all_closed.xlsx
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 18:07</t>
+          <t>Last run: 23Apr2026 21:48</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Last run: 23Apr2026 18:07</t>
+          <t>Last run: 23Apr2026 21:48</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>Dose form 'INJECTION' not in allowed list (CAPSULE/TABLET) for treatment: DRUG A 20MG at visit END OF TREATMENT</t>
+          <t>Dose form 'INJECTION' not in allowed list (TABLET/CAPSULE) for treatment: DRUG A 20MG at visit END OF TREATMENT</t>
         </is>
       </c>
       <c r="E5" s="8" t="n">
